--- a/solucao1_solver.xlsx
+++ b/solucao1_solver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nilbe\Documents\DISCIPLINAS\TCC2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{0E6B8A72-C16A-43FC-A80C-7C49E00EE1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44972BC1-D7ED-43E9-BE27-AF48A1036ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{F5B76033-715A-4D61-ACFB-271E9F0509A6}"/>
   </bookViews>
@@ -127,7 +127,6 @@
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -573,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -586,9 +585,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -604,10 +600,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -619,6 +612,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,21 +938,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -964,17 +960,17 @@
       <c r="B3" s="2">
         <v>850</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>0.62</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <f>5.630682+0.001894</f>
         <v>5.6325760000000002</v>
       </c>
-      <c r="G3" s="8">
-        <f>F3/C3</f>
+      <c r="G3" s="7">
+        <f t="shared" ref="G3:G8" si="0">F3/C3</f>
         <v>9.0848000000000013</v>
       </c>
       <c r="I3" t="s">
@@ -985,16 +981,16 @@
       <c r="B4" s="2">
         <v>854</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>2.1800000000000002</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>11.75</v>
       </c>
-      <c r="G4" s="8">
-        <f>F4/C4</f>
+      <c r="G4" s="7">
+        <f t="shared" si="0"/>
         <v>5.3899082568807337</v>
       </c>
       <c r="I4" t="s">
@@ -1005,16 +1001,16 @@
       <c r="B5" s="2">
         <v>822</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>3</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>17.739999999999998</v>
       </c>
-      <c r="G5" s="8">
-        <f>F5/C5</f>
+      <c r="G5" s="7">
+        <f t="shared" si="0"/>
         <v>5.9133333333333331</v>
       </c>
       <c r="I5" t="s">
@@ -1025,16 +1021,16 @@
       <c r="B6" s="2">
         <v>834</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>4.05</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>20.76</v>
       </c>
-      <c r="G6" s="8">
-        <f>F6/C6</f>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
         <v>5.1259259259259267</v>
       </c>
       <c r="I6" t="s">
@@ -1045,16 +1041,16 @@
       <c r="B7" s="2">
         <v>840</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>6.75</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>21.82</v>
       </c>
-      <c r="G7" s="8">
-        <f>F7/C7</f>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
         <v>3.2325925925925927</v>
       </c>
       <c r="I7" t="s">
@@ -1065,16 +1061,16 @@
       <c r="B8" s="2">
         <v>848</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>7.47</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>21.86</v>
       </c>
-      <c r="G8" s="8">
-        <f>F8/C8</f>
+      <c r="G8" s="7">
+        <f t="shared" si="0"/>
         <v>2.9263721552878179</v>
       </c>
       <c r="I8" t="s">
@@ -1082,7 +1078,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="9"/>
+      <c r="B15" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1103,21 +1099,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="10"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="6"/>
+      <c r="P1" s="5"/>
       <c r="S1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1128,24 +1124,24 @@
         <v>78</v>
       </c>
       <c r="X1" s="1"/>
-      <c r="Y1" s="6"/>
+      <c r="Y1" s="5"/>
     </row>
     <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="11"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="7"/>
+      <c r="P2" s="6"/>
       <c r="S2" s="2">
         <v>850</v>
       </c>
@@ -1157,29 +1153,29 @@
         <v>0</v>
       </c>
       <c r="X2" s="2"/>
-      <c r="Y2" s="7"/>
+      <c r="Y2" s="6"/>
       <c r="Z2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="11"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="7"/>
+      <c r="P3" s="6"/>
       <c r="S3" s="2">
         <v>854</v>
       </c>
@@ -1191,27 +1187,27 @@
         <v>0</v>
       </c>
       <c r="X3" s="2"/>
-      <c r="Y3" s="7"/>
+      <c r="Y3" s="6"/>
       <c r="Z3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="11"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="7"/>
+      <c r="P4" s="6"/>
       <c r="S4" s="2">
         <v>822</v>
       </c>
@@ -1219,27 +1215,27 @@
         <v>3</v>
       </c>
       <c r="X4" s="2"/>
-      <c r="Y4" s="7"/>
+      <c r="Y4" s="6"/>
       <c r="Z4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="11"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="7"/>
+      <c r="P5" s="6"/>
       <c r="S5" s="2">
         <v>834</v>
       </c>
@@ -1247,27 +1243,27 @@
         <v>4.05</v>
       </c>
       <c r="X5" s="2"/>
-      <c r="Y5" s="7"/>
+      <c r="Y5" s="6"/>
       <c r="Z5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="11"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="7"/>
+      <c r="P6" s="6"/>
       <c r="S6" s="2">
         <v>840</v>
       </c>
@@ -1275,27 +1271,27 @@
         <v>6.75</v>
       </c>
       <c r="X6" s="2"/>
-      <c r="Y6" s="7"/>
+      <c r="Y6" s="6"/>
       <c r="Z6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="11"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="7"/>
+      <c r="P7" s="6"/>
       <c r="S7" s="2">
         <v>848</v>
       </c>
@@ -1303,20 +1299,20 @@
         <v>7.47</v>
       </c>
       <c r="X7" s="2"/>
-      <c r="Y7" s="7"/>
+      <c r="Y7" s="6"/>
       <c r="Z7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="11"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1324,14 +1320,14 @@
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="11"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1339,14 +1335,14 @@
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="11"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1364,14 +1360,14 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="11"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1379,14 +1375,14 @@
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="11"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -1394,14 +1390,14 @@
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="11"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1409,14 +1405,14 @@
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="11"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1424,14 +1420,14 @@
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="11"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="10"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1439,14 +1435,14 @@
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="11"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1454,14 +1450,14 @@
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="11"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="10"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1469,14 +1465,14 @@
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="11"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1484,14 +1480,14 @@
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="11"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1499,14 +1495,14 @@
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="11"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="10"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1514,14 +1510,14 @@
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="11"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1529,14 +1525,14 @@
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="11"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1544,14 +1540,14 @@
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="11"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -1559,14 +1555,14 @@
       <c r="M23" s="2"/>
     </row>
     <row r="24" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="11"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1574,14 +1570,14 @@
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="11"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="10"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1589,14 +1585,14 @@
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="11"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="10"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1604,14 +1600,14 @@
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="11"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="10"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1619,14 +1615,14 @@
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="11"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1634,14 +1630,14 @@
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="11"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="10"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -1649,14 +1645,14 @@
       <c r="M29" s="2"/>
     </row>
     <row r="30" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="11"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="10"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -1664,14 +1660,14 @@
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="11"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="10"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1679,14 +1675,14 @@
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="11"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="10"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -1694,14 +1690,14 @@
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="11"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="10"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -3050,177 +3046,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="7:21" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="17">
-        <v>3</v>
-      </c>
-      <c r="I1" s="17" t="s">
+      <c r="H1" s="15">
+        <v>3</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="17">
+      <c r="K1" s="15">
         <v>300</v>
       </c>
-      <c r="L1" s="17">
+      <c r="L1" s="15">
         <v>0</v>
       </c>
-      <c r="M1" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O1" s="6" t="s">
+      <c r="M1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="7:21" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="17">
-        <v>3</v>
-      </c>
-      <c r="I2" s="17" t="s">
+      <c r="H2" s="15">
+        <v>3</v>
+      </c>
+      <c r="I2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="15">
         <v>300</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="15">
         <v>0</v>
       </c>
-      <c r="M2" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" s="7">
+      <c r="M2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="6">
         <v>0.62</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="7">
+      <c r="R2" s="6">
         <f>5.630682+0.001894</f>
         <v>5.6325760000000002</v>
       </c>
-      <c r="S2" s="8"/>
-      <c r="U2" s="14">
+      <c r="S2" s="7"/>
+      <c r="U2" s="12">
         <f>L6+ L7</f>
         <v>0.62000000002059563</v>
       </c>
     </row>
     <row r="3" spans="7:21" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="17">
-        <v>3</v>
-      </c>
-      <c r="I3" s="17" t="s">
+      <c r="H3" s="15">
+        <v>3</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="15">
         <v>300</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="15">
         <v>0</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="7">
+      <c r="M3" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="6">
         <v>2.1800000000000002</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="7">
+      <c r="R3" s="6">
         <v>11.75</v>
       </c>
-      <c r="S3" s="8"/>
-      <c r="U3" s="14">
+      <c r="S3" s="7"/>
+      <c r="U3" s="12">
         <f>L6+L7 +L24 +L9 +L13+ L14+ L15</f>
         <v>2.1800000000005557</v>
       </c>
     </row>
     <row r="4" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="15">
         <v>1</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="15">
         <v>808.2</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="15">
         <v>810.2</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="15">
         <v>303</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="15">
         <v>0</v>
       </c>
-      <c r="M4" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="7">
+      <c r="M4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="6">
         <v>3</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="7">
+      <c r="R4" s="6">
         <v>17.739999999999998</v>
       </c>
-      <c r="S4" s="8"/>
-      <c r="U4" s="14">
+      <c r="S4" s="7"/>
+      <c r="U4" s="12">
         <f>L6+ L7+ L24+ L8+ L10+ L11</f>
         <v>2.9999999999740177</v>
       </c>
     </row>
     <row r="5" spans="7:21" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="17">
-        <v>3</v>
-      </c>
-      <c r="I5" s="17" t="s">
+      <c r="H5" s="15">
+        <v>3</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="15">
         <v>300</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="15">
         <v>0</v>
       </c>
-      <c r="M5" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="7">
+      <c r="M5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="6">
         <v>4.05</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="7">
+      <c r="R5" s="6">
         <v>20.76</v>
       </c>
-      <c r="S5" s="8"/>
-      <c r="U5" s="14">
+      <c r="S5" s="7"/>
+      <c r="U5" s="12">
         <f>L6+ L7+ L24+ L9+ L13+ L14 +L15 +L27+ L25+ L16+ L29</f>
         <v>4.0499999998571639</v>
       </c>
@@ -3247,16 +3243,16 @@
       <c r="M6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="6">
         <v>6.75</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="7">
+      <c r="R6" s="6">
         <v>21.82</v>
       </c>
-      <c r="S6" s="8"/>
-      <c r="U6" s="14">
+      <c r="S6" s="7"/>
+      <c r="U6" s="12">
         <f>L6+ L7 +L24+ L9+ L13+ L14+ L15+ L27+ L25+ L16+ L29+  L17+ L30+ L19</f>
         <v>6.7500000001666089</v>
       </c>
@@ -3283,16 +3279,16 @@
       <c r="M7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="6">
         <v>7.47</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <v>21.86</v>
       </c>
-      <c r="S7" s="8"/>
-      <c r="U7" s="14">
+      <c r="S7" s="7"/>
+      <c r="U7" s="12">
         <f>L6+L7+L24+L9+L13+L14+L15+L27+L25+L16+L29+L18+L21+L22+L23</f>
         <v>7.4699999974422795</v>
       </c>
@@ -3342,10 +3338,10 @@
       <c r="M9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="T9" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="U9" s="15">
+      <c r="U9" s="13">
         <f>SUM(L1:L32)</f>
         <v>10.989999998715993</v>
       </c>
@@ -3615,7 +3611,7 @@
       <c r="M19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P19" s="18">
+      <c r="P19" s="16">
         <f>SUM(P14:P18)</f>
         <v>3.3155300000000003</v>
       </c>
